--- a/lista.xlsx
+++ b/lista.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eco_x\Downloads\Phone Link\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b13b68726d4d8989/ARCHIVOS XAVIER/APS/Virgen Maria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC37B56E-BF35-4053-A48E-ECF05B896C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{5C7F9D3D-B469-4DD7-AE72-59DFFA54B49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C607ABE4-8EC5-4951-A7F6-F54C691BCD5A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B8ADF1EA-8CC5-4C57-B17E-5279ED80BB0E}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="lista" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">lista!$A$1:$E$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">lista!$A$1:$E$114</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -83,12 +83,6 @@
     <t xml:space="preserve">SUE ESCOBAR BALDEON </t>
   </si>
   <si>
-    <t>0980006360</t>
-  </si>
-  <si>
-    <t>suescobar87@gmail.com</t>
-  </si>
-  <si>
     <t>GESTIÓN TRIBUTARIA</t>
   </si>
   <si>
@@ -146,10 +140,6 @@
     <t>0993152262</t>
   </si>
   <si>
-    <t xml:space="preserve">rosaura_katty@hotmail.com
- </t>
-  </si>
-  <si>
     <t>ILEANA REYES</t>
   </si>
   <si>
@@ -183,9 +173,6 @@
     <t>johanapamela@hotmail.com</t>
   </si>
   <si>
-    <t>JURIDICO</t>
-  </si>
-  <si>
     <t>VELYALLINE ROMO</t>
   </si>
   <si>
@@ -495,9 +482,6 @@
     <t>jumapi97@gmail.com</t>
   </si>
   <si>
-    <t>MARIANELA  POZO</t>
-  </si>
-  <si>
     <t>0995471084</t>
   </si>
   <si>
@@ -537,9 +521,6 @@
     <t>CONTROL DE CATASTROS Y DEBERES FORMALES</t>
   </si>
   <si>
-    <t xml:space="preserve">ROSA MARÍA RIVERA </t>
-  </si>
-  <si>
     <t>0969184596</t>
   </si>
   <si>
@@ -598,6 +579,24 @@
   </si>
   <si>
     <t>krol.sm@hotmail.com</t>
+  </si>
+  <si>
+    <t>0985729586</t>
+  </si>
+  <si>
+    <t>FATIMA SABANDO</t>
+  </si>
+  <si>
+    <t>NATHALIA PINOS</t>
+  </si>
+  <si>
+    <t>MARIANELA POZO</t>
+  </si>
+  <si>
+    <t>ROSA MARÍA RIVERA</t>
+  </si>
+  <si>
+    <t>rosaura_katty@hotmail.com</t>
   </si>
 </sst>
 </file>
@@ -689,7 +688,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -729,6 +728,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1088,19 +1090,19 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="13">
-        <v>46056</v>
+        <v>46146</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>5</v>
@@ -1108,19 +1110,19 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="14">
-        <v>46057</v>
+        <v>46147</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>9</v>
@@ -1128,19 +1130,19 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
-        <v>46058</v>
+        <v>46148</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>13</v>
@@ -1148,575 +1150,575 @@
     </row>
     <row r="5" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14">
-        <v>46059</v>
+        <v>46149</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>23</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E5" s="4"/>
       <c r="K5" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
-        <v>46062</v>
+        <v>46150</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
-        <v>46063</v>
+        <v>46153</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="4"/>
+        <v>185</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="K7" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
-        <v>46064</v>
+        <v>46154</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
-        <v>46065</v>
+        <v>46155</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
-        <v>46066</v>
+        <v>46156</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
-        <v>46071</v>
+        <v>46157</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
-        <v>46072</v>
+        <v>46160</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>47</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
-        <v>46073</v>
+        <v>46161</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
-        <v>46076</v>
+        <v>46162</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="K14" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
-        <v>46077</v>
+        <v>46163</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>55</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
-        <v>46078</v>
+        <v>46164</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="14">
-        <v>46079</v>
+        <v>46168</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0</v>
-      </c>
-      <c r="D17" s="4"/>
+        <v>181</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
-        <v>46080</v>
+        <v>46169</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="14">
-        <v>46083</v>
+        <v>46170</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>23</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="E19" s="4"/>
       <c r="K19" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
-        <v>46084</v>
+        <v>46171</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
-        <v>46085</v>
+        <v>46174</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="K21" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
-        <v>46086</v>
+        <v>46175</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>78</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D22" s="4"/>
       <c r="E22" s="4" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
-        <v>46087</v>
+        <v>46176</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="K23" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
-        <v>46090</v>
+        <v>46177</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="4"/>
+        <v>85</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="E24" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14">
-        <v>46091</v>
+        <v>46178</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
-        <v>46092</v>
+        <v>46181</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14">
-        <v>46093</v>
+        <v>46182</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="E27" s="4" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
-        <v>46094</v>
+        <v>46183</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14">
-        <v>46097</v>
+        <v>46184</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14">
-        <v>46098</v>
+        <v>46185</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14">
-        <v>46099</v>
+        <v>46188</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14">
-        <v>46100</v>
+        <v>46189</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>109</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14">
-        <v>46101</v>
+        <v>46190</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>111</v>
+        <v>38</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14">
-        <v>46104</v>
+        <v>46191</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>114</v>
@@ -1728,331 +1730,329 @@
         <v>116</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14">
-        <v>46105</v>
+        <v>46192</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>117</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="14">
-        <v>46106</v>
+        <v>46195</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>120</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D36" s="4"/>
       <c r="E36" s="4" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="14">
-        <v>46107</v>
+        <v>46196</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>121</v>
+        <v>182</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="14">
-        <v>46108</v>
+        <v>46197</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D38" s="4"/>
+        <v>127</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="E38" s="4" t="s">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14">
-        <v>46111</v>
+        <v>46198</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="14">
-        <v>46112</v>
+        <v>46199</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="14">
-        <v>46113</v>
+        <v>46202</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="14">
-        <v>46114</v>
+        <v>46203</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="14">
-        <v>46118</v>
+        <v>46204</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>141</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="D43" s="4"/>
       <c r="E43" s="4" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="14">
-        <v>46119</v>
+        <v>46205</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="14">
-        <v>46120</v>
+        <v>46206</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="D45" s="4"/>
+        <v>147</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>148</v>
+      </c>
       <c r="E45" s="4" t="s">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="14">
-        <v>46121</v>
+        <v>46209</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="14">
-        <v>46122</v>
+        <v>46210</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="14">
-        <v>46125</v>
+        <v>46211</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="14">
-        <v>46126</v>
+        <v>46212</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="14">
-        <v>46127</v>
+        <v>46213</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C50" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>164</v>
-      </c>
       <c r="K50" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A51" s="14">
-        <v>46128</v>
+        <v>46216</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>165</v>
@@ -2064,33 +2064,35 @@
         <v>167</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="14">
-        <v>46129</v>
+        <v>46217</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="D52" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D52" s="4"/>
       <c r="E52" s="4" t="s">
-        <v>168</v>
+        <v>8</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="14">
-        <v>46132</v>
+        <v>46218</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>171</v>
@@ -2102,15 +2104,15 @@
         <v>173</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>168</v>
+        <v>47</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="14">
-        <v>46133</v>
+        <v>46219</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>174</v>
@@ -2122,15 +2124,15 @@
         <v>176</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="14">
-        <v>46134</v>
+        <v>46220</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>177</v>
@@ -2142,181 +2144,181 @@
         <v>179</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="14">
-        <v>46135</v>
+        <v>46223</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>181</v>
+        <v>6</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>182</v>
+        <v>7</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="14">
-        <v>46136</v>
+        <v>46224</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>183</v>
+        <v>9</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>185</v>
+        <v>11</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="14">
-        <v>46139</v>
+        <v>46225</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="14">
-        <v>46140</v>
+        <v>46226</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="14">
-        <v>46141</v>
+        <v>46230</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C60" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="14">
-        <v>46142</v>
+        <v>46231</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>16</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E61" s="4"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="14">
-        <v>46146</v>
+        <v>46232</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="14">
-        <v>46147</v>
+        <v>46233</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>26</v>
+        <v>185</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="14">
-        <v>46148</v>
+        <v>46234</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E64" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="14">
         <v>46149</v>
       </c>
       <c r="B65" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="E65" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2324,16 +2326,16 @@
         <v>46150</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2341,16 +2343,16 @@
         <v>46153</v>
       </c>
       <c r="B67" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
@@ -2358,16 +2360,16 @@
         <v>46154</v>
       </c>
       <c r="B68" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E68" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="F68" s="11"/>
     </row>
@@ -2376,13 +2378,13 @@
         <v>46155</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>47</v>
@@ -2393,16 +2395,16 @@
         <v>46156</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2410,7 +2412,7 @@
         <v>46157</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>10</v>
@@ -2419,7 +2421,7 @@
         <v>11</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -2427,16 +2429,16 @@
         <v>46160</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -2444,16 +2446,16 @@
         <v>46161</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -2461,14 +2463,14 @@
         <v>46162</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C74" s="5">
         <v>0</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -2476,16 +2478,16 @@
         <v>46163</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -2493,16 +2495,16 @@
         <v>46164</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>66</v>
+        <v>181</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2510,16 +2512,16 @@
         <v>46168</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -2527,13 +2529,13 @@
         <v>46169</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E78" s="4"/>
     </row>
@@ -2542,16 +2544,16 @@
         <v>46170</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -2559,16 +2561,16 @@
         <v>46171</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2576,14 +2578,14 @@
         <v>46174</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2591,14 +2593,14 @@
         <v>46175</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -2606,16 +2608,16 @@
         <v>46176</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -2623,14 +2625,14 @@
         <v>46177</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2638,16 +2640,16 @@
         <v>46178</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -2655,16 +2657,16 @@
         <v>46181</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -2672,16 +2674,16 @@
         <v>46182</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -2689,16 +2691,16 @@
         <v>46183</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -2706,16 +2708,16 @@
         <v>46184</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -2723,16 +2725,16 @@
         <v>46185</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2740,16 +2742,16 @@
         <v>46188</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -2757,16 +2759,16 @@
         <v>46189</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -2774,16 +2776,16 @@
         <v>46190</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -2791,13 +2793,13 @@
         <v>46191</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>8</v>
@@ -2808,14 +2810,14 @@
         <v>46192</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -2823,13 +2825,13 @@
         <v>46195</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>8</v>
@@ -2840,16 +2842,16 @@
         <v>46196</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -2857,13 +2859,13 @@
         <v>46197</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>8</v>
@@ -2874,13 +2876,13 @@
         <v>46198</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>8</v>
@@ -2891,16 +2893,16 @@
         <v>46199</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -2908,16 +2910,16 @@
         <v>46202</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -2925,14 +2927,14 @@
         <v>46203</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -2940,16 +2942,16 @@
         <v>46204</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -2957,16 +2959,16 @@
         <v>46205</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -2974,16 +2976,16 @@
         <v>46206</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -2991,16 +2993,16 @@
         <v>46209</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -3008,16 +3010,16 @@
         <v>46210</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
@@ -3025,16 +3027,16 @@
         <v>46211</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -3042,14 +3044,14 @@
         <v>46212</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D109" s="4"/>
       <c r="E109" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -3057,16 +3059,16 @@
         <v>46213</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -3074,13 +3076,13 @@
         <v>46216</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>8</v>
@@ -3091,16 +3093,16 @@
         <v>46217</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -3108,16 +3110,16 @@
         <v>46218</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -3125,23 +3127,23 @@
         <v>46219</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E74" xr:uid="{CEDA76FD-D543-4218-8821-AEE3CE2CEA86}"/>
+  <autoFilter ref="A1:E114" xr:uid="{CEDA76FD-D543-4218-8821-AEE3CE2CEA86}"/>
   <conditionalFormatting sqref="K2:K56">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/lista.xlsx
+++ b/lista.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b13b68726d4d8989/ARCHIVOS XAVIER/APS/Virgen Maria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{5C7F9D3D-B469-4DD7-AE72-59DFFA54B49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C607ABE4-8EC5-4951-A7F6-F54C691BCD5A}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{5C7F9D3D-B469-4DD7-AE72-59DFFA54B49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C3B88BA-C525-4E7E-9DDA-BC2C602616CC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B8ADF1EA-8CC5-4C57-B17E-5279ED80BB0E}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="lista" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">lista!$A$1:$E$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">lista!$A$1:$E$115</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="189">
   <si>
     <t>Fecha</t>
   </si>
@@ -597,6 +597,15 @@
   </si>
   <si>
     <t>rosaura_katty@hotmail.com</t>
+  </si>
+  <si>
+    <t>SUE ESCOBAR BALDEON</t>
+  </si>
+  <si>
+    <t>0980006360</t>
+  </si>
+  <si>
+    <t>suescobar87@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1058,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92574074-88DB-4446-9761-6F1FEA06A5BF}">
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="12" customWidth="1"/>
@@ -1089,17 +1098,17 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="13">
-        <v>46146</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
+      <c r="A2" s="14">
+        <v>46141</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>186</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>16</v>
+        <v>187</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>14</v>
@@ -1109,20 +1118,20 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="14">
-        <v>46147</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>19</v>
+      <c r="A3" s="13">
+        <v>46146</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>9</v>
@@ -1130,19 +1139,19 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
-        <v>46148</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>23</v>
+        <v>46147</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>13</v>
@@ -1150,54 +1159,54 @@
     </row>
     <row r="5" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="K5" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>14</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E6" s="4"/>
       <c r="K6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>185</v>
+        <v>30</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>14</v>
@@ -1208,19 +1217,19 @@
     </row>
     <row r="8" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
-        <v>46154</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>33</v>
+        <v>46153</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>25</v>
@@ -1228,19 +1237,19 @@
     </row>
     <row r="9" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>28</v>
@@ -1248,19 +1257,19 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
-        <v>46156</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>41</v>
+        <v>46155</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>31</v>
@@ -1268,16 +1277,16 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>47</v>
@@ -1288,16 +1297,16 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
-        <v>46160</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>48</v>
+        <v>46157</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>47</v>
@@ -1308,19 +1317,19 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
-        <v>46161</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>49</v>
+        <v>46160</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>41</v>
@@ -1328,16 +1337,16 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
-        <v>46162</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>53</v>
+        <v>46161</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>52</v>
@@ -1348,17 +1357,19 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
-        <v>46163</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="5">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4"/>
+        <v>46162</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="E15" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>48</v>
@@ -1366,19 +1377,17 @@
     </row>
     <row r="16" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>60</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>49</v>
@@ -1386,19 +1395,19 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="14">
-        <v>46168</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>181</v>
+        <v>46164</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" t="s">
-        <v>21</v>
+        <v>60</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>53</v>
@@ -1406,19 +1415,19 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>65</v>
+        <v>181</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
+      </c>
+      <c r="E18" t="s">
+        <v>21</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>56</v>
@@ -1426,57 +1435,57 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="14">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="K19" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="E20" s="4"/>
       <c r="K20" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>65</v>
@@ -1484,17 +1493,19 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="E22" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>69</v>
@@ -1502,13 +1513,13 @@
     </row>
     <row r="23" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4" t="s">
@@ -1520,17 +1531,15 @@
     </row>
     <row r="24" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>86</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
         <v>81</v>
       </c>
@@ -1540,17 +1549,19 @@
     </row>
     <row r="25" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" s="4"/>
+        <v>85</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="E25" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>33</v>
@@ -1558,19 +1569,17 @@
     </row>
     <row r="26" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>92</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>79</v>
@@ -1578,16 +1587,16 @@
     </row>
     <row r="27" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>81</v>
@@ -1598,16 +1607,16 @@
     </row>
     <row r="28" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>81</v>
@@ -1618,16 +1627,16 @@
     </row>
     <row r="29" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>81</v>
@@ -1638,19 +1647,19 @@
     </row>
     <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>90</v>
@@ -1658,19 +1667,19 @@
     </row>
     <row r="31" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>93</v>
@@ -1678,16 +1687,16 @@
     </row>
     <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>109</v>
@@ -1698,19 +1707,19 @@
     </row>
     <row r="33" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>99</v>
@@ -1718,19 +1727,19 @@
     </row>
     <row r="34" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>102</v>
@@ -1738,19 +1747,19 @@
     </row>
     <row r="35" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>106</v>
@@ -1758,17 +1767,19 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="14">
-        <v>46195</v>
+        <v>46192</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D36" s="4"/>
+        <v>118</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="E36" s="4" t="s">
-        <v>122</v>
+        <v>8</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>110</v>
@@ -1776,19 +1787,17 @@
     </row>
     <row r="37" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="14">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>182</v>
+        <v>120</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>125</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D37" s="4"/>
       <c r="E37" s="4" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>15</v>
@@ -1796,19 +1805,19 @@
     </row>
     <row r="38" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="14">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>18</v>
@@ -1816,19 +1825,19 @@
     </row>
     <row r="39" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>22</v>
@@ -1836,16 +1845,16 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="14">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>8</v>
@@ -1856,19 +1865,19 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="14">
-        <v>46202</v>
+        <v>46199</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>122</v>
+        <v>8</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>28</v>
@@ -1876,19 +1885,19 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="14">
-        <v>46203</v>
+        <v>46202</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>31</v>
@@ -1896,17 +1905,19 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="14">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="D43" s="4"/>
+        <v>138</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="E43" s="4" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>48</v>
@@ -1914,19 +1925,17 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="14">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>146</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>113</v>
@@ -1934,19 +1943,19 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="14">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>41</v>
@@ -1954,19 +1963,19 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="14">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>150</v>
+        <v>183</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>152</v>
+        <v>36</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>114</v>
@@ -1974,19 +1983,19 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="14">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>44</v>
@@ -1994,19 +2003,19 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="14">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>49</v>
@@ -2014,19 +2023,19 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="14">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>56</v>
@@ -2034,15 +2043,17 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="14">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D50" s="4"/>
+        <v>160</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E50" s="4" t="s">
         <v>162</v>
       </c>
@@ -2050,41 +2061,39 @@
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="14">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="E51" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4" t="s">
         <v>162</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A52" s="14">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>8</v>
+        <v>167</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>162</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>120</v>
@@ -2092,19 +2101,19 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="14">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>172</v>
+        <v>168</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>169</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>123</v>
@@ -2112,19 +2121,19 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="14">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>172</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>126</v>
@@ -2132,19 +2141,19 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="14">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>129</v>
@@ -2152,19 +2161,19 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="14">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>6</v>
+        <v>178</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>7</v>
+        <v>179</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>132</v>
@@ -2172,116 +2181,116 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="14">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>180</v>
+        <v>6</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="14">
-        <v>46225</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>16</v>
+        <v>46224</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="14">
-        <v>46226</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>19</v>
+        <v>46225</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="14">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="14">
-        <v>46231</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>25</v>
+        <v>46230</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E61" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="14">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>14</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E62" s="4"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="14">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>185</v>
+        <v>30</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>14</v>
@@ -2289,50 +2298,50 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="14">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="14">
-        <v>46149</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>28</v>
+        <v>46234</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="14">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>185</v>
+        <v>30</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>14</v>
@@ -2340,68 +2349,68 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="14">
-        <v>46153</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>33</v>
+        <v>46150</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A68" s="14">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F68" s="11"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="14">
-        <v>46155</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>41</v>
+        <v>46154</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="14">
-        <v>46156</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>44</v>
+        <v>46155</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>47</v>
@@ -2409,16 +2418,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="14">
-        <v>46157</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>48</v>
+        <v>46156</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>47</v>
@@ -2426,33 +2435,33 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="14">
-        <v>46160</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>49</v>
+        <v>46157</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="14">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>52</v>
@@ -2460,143 +2469,145 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="14">
-        <v>46162</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C74" s="5">
-        <v>0</v>
-      </c>
-      <c r="D74" s="4"/>
-      <c r="E74" t="s">
-        <v>57</v>
+        <v>46161</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="14">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
+      </c>
+      <c r="C75" s="5">
+        <v>0</v>
+      </c>
+      <c r="D75" s="4"/>
+      <c r="E75" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="14">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="14">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>65</v>
+        <v>181</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="14">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E78" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="14">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="E79" s="4"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="14">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="14">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D81" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="E81" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="14">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="4" t="s">
@@ -2605,65 +2616,63 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="14">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>86</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="D83" s="4"/>
       <c r="E83" s="4" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="14">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D84" s="4"/>
+        <v>85</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="E84" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="14">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>92</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D85" s="4"/>
       <c r="E85" s="4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="14">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>81</v>
@@ -2671,16 +2680,16 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="14">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>81</v>
@@ -2688,16 +2697,16 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="14">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>81</v>
@@ -2705,50 +2714,50 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="14">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="14">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="14">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>111</v>
+        <v>106</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>109</v>
@@ -2756,133 +2765,133 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="14">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>38</v>
+        <v>110</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="14">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="14">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="14">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D95" s="4"/>
+        <v>118</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="E95" s="4" t="s">
-        <v>122</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="14">
-        <v>46195</v>
+        <v>46192</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>125</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D96" s="4"/>
       <c r="E96" s="4" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="14">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>127</v>
+        <v>182</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="14">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="14">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>8</v>
@@ -2890,260 +2899,277 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="14">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>122</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="14">
-        <v>46202</v>
+        <v>46199</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="14">
-        <v>46203</v>
+        <v>46202</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C102" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D102" s="4"/>
+        <v>138</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="E102" s="4" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="14">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D103" s="4"/>
       <c r="E103" s="4" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="14">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="14">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>152</v>
+        <v>36</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="14">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="14">
+        <v>46209</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="14">
         <v>46210</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B108" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C108" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="D108" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E107" s="4" t="s">
+      <c r="E108" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A108" s="14">
+    <row r="109" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A109" s="14">
         <v>46211</v>
       </c>
-      <c r="B108" s="6" t="s">
+      <c r="B109" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C108" s="8" t="s">
+      <c r="C109" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D109" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E108" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="14">
-        <v>46212</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D109" s="4"/>
-      <c r="E109" s="4" t="s">
+      <c r="E109" s="10" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="14">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>167</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D110" s="4"/>
       <c r="E110" s="4" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="14">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>166</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>8</v>
+        <v>162</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="14">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="14">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="14">
+        <v>46218</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="14">
         <v>46219</v>
       </c>
-      <c r="B114" s="6" t="s">
+      <c r="B115" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C114" s="8" t="s">
+      <c r="C115" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="D115" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E114" s="4" t="s">
+      <c r="E115" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" s="14"/>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E114" xr:uid="{CEDA76FD-D543-4218-8821-AEE3CE2CEA86}"/>
+  <autoFilter ref="A1:E115" xr:uid="{CEDA76FD-D543-4218-8821-AEE3CE2CEA86}"/>
   <conditionalFormatting sqref="K2:K56">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/lista.xlsx
+++ b/lista.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b13b68726d4d8989/ARCHIVOS XAVIER/APS/Virgen Maria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{5C7F9D3D-B469-4DD7-AE72-59DFFA54B49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB0F01A9-2822-4DF0-9A9A-5A6E181BBFC8}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{5C7F9D3D-B469-4DD7-AE72-59DFFA54B49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4543360-9C8E-443C-B711-9807BF2EB0D3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B8ADF1EA-8CC5-4C57-B17E-5279ED80BB0E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="187">
   <si>
     <t>Fecha</t>
   </si>
@@ -593,7 +593,13 @@
     <t>rosaura_katty@hotmail.com</t>
   </si>
   <si>
-    <t>0</t>
+    <t>SUE ESCOBAR BALDEON</t>
+  </si>
+  <si>
+    <t>0980006360</t>
+  </si>
+  <si>
+    <t>suescobar87@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -680,7 +686,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -704,11 +710,6 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -718,13 +719,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1081,19 +1075,19 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="14">
+      <c r="A2" s="11">
         <v>46141</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>15</v>
+      <c r="B2" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="K2" s="4" t="s">
@@ -1101,97 +1095,97 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="14">
+      <c r="A3" s="11">
         <v>46146</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>18</v>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="14">
+      <c r="A4" s="11">
         <v>46147</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>22</v>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>14</v>
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+      <c r="A5" s="11">
         <v>46148</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>25</v>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="K5" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="14">
+      <c r="A6" s="11">
         <v>46149</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>28</v>
+      <c r="B6" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>14</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="4"/>
       <c r="K6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="11">
         <v>46150</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>31</v>
+      <c r="B7" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="K7" s="4" t="s">
@@ -1199,79 +1193,79 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14">
+      <c r="A8" s="11">
         <v>46153</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>33</v>
+      <c r="B8" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
+      <c r="A9" s="11">
         <v>46154</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>37</v>
+      <c r="B9" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
+      <c r="A10" s="11">
         <v>46155</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>41</v>
+      <c r="B10" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>47</v>
+        <v>38</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="14">
+      <c r="A11" s="11">
         <v>46156</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>44</v>
+      <c r="B11" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>47</v>
       </c>
       <c r="K11" s="4" t="s">
@@ -1279,19 +1273,19 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="14">
+      <c r="A12" s="11">
         <v>46157</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>48</v>
+      <c r="B12" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>47</v>
       </c>
       <c r="K12" s="4" t="s">
@@ -1299,39 +1293,39 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
+      <c r="A13" s="11">
         <v>46160</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>49</v>
+      <c r="B13" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>52</v>
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="14">
+      <c r="A14" s="11">
         <v>46161</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>53</v>
+      <c r="B14" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="4" t="s">
@@ -1339,171 +1333,173 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
+      <c r="A15" s="11">
         <v>46162</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>56</v>
+      <c r="B15" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" t="s">
+        <v>52</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="14">
+      <c r="A16" s="11">
         <v>46163</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>61</v>
+      <c r="B16" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="14">
+      <c r="A17" s="11">
         <v>46164</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>179</v>
+      <c r="B17" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>21</v>
+        <v>59</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="14">
+      <c r="A18" s="11">
         <v>46168</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>65</v>
+      <c r="B18" s="5" t="s">
+        <v>179</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="14">
+      <c r="A19" s="11">
         <v>46169</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>69</v>
+      <c r="B19" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="10"/>
+        <v>66</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="K19" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="14">
+      <c r="A20" s="11">
         <v>46170</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>72</v>
+      <c r="B20" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>68</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="4"/>
       <c r="K20" s="5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14">
+      <c r="A21" s="11">
         <v>46171</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>75</v>
+      <c r="B21" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="K21" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="14">
+      <c r="A22" s="11">
         <v>46174</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>79</v>
+      <c r="B22" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10" t="s">
-        <v>81</v>
+        <v>76</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14">
+      <c r="A23" s="11">
         <v>46175</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>82</v>
+      <c r="B23" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
         <v>81</v>
       </c>
       <c r="K23" s="5" t="s">
@@ -1511,19 +1507,17 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="14">
+      <c r="A24" s="11">
         <v>46176</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>84</v>
+      <c r="B24" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4" t="s">
         <v>81</v>
       </c>
       <c r="K24" s="5" t="s">
@@ -1531,57 +1525,57 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="14">
+      <c r="A25" s="11">
         <v>46177</v>
       </c>
-      <c r="B25" s="11" t="s">
-        <v>87</v>
+      <c r="B25" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10" t="s">
-        <v>89</v>
+        <v>85</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="14">
+      <c r="A26" s="11">
         <v>46178</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>90</v>
+      <c r="B26" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>81</v>
+        <v>88</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="14">
+      <c r="A27" s="11">
         <v>46181</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>93</v>
+      <c r="B27" s="5" t="s">
+        <v>90</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E27" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>81</v>
       </c>
       <c r="K27" s="5" t="s">
@@ -1589,19 +1583,19 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="14">
+      <c r="A28" s="11">
         <v>46182</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>96</v>
+      <c r="B28" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>81</v>
       </c>
       <c r="K28" s="5" t="s">
@@ -1609,19 +1603,19 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="14">
+      <c r="A29" s="11">
         <v>46183</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>99</v>
+      <c r="B29" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>81</v>
       </c>
       <c r="K29" s="5" t="s">
@@ -1629,59 +1623,59 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="14">
+      <c r="A30" s="11">
         <v>46184</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>102</v>
+      <c r="B30" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>105</v>
+        <v>100</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="14">
+      <c r="A31" s="11">
         <v>46185</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>106</v>
+      <c r="B31" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>109</v>
+        <v>103</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K31" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="14">
+      <c r="A32" s="11">
         <v>46188</v>
       </c>
-      <c r="B32" s="11" t="s">
-        <v>110</v>
+      <c r="B32" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="E32" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>109</v>
       </c>
       <c r="K32" s="5" t="s">
@@ -1689,137 +1683,137 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="14">
+      <c r="A33" s="11">
         <v>46189</v>
       </c>
-      <c r="B33" s="11" t="s">
-        <v>113</v>
+      <c r="B33" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>40</v>
+        <v>111</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="K33" s="5" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="14">
+      <c r="A34" s="11">
         <v>46190</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>115</v>
+      <c r="B34" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>8</v>
+        <v>38</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="K34" s="5" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="14">
+      <c r="A35" s="11">
         <v>46191</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>118</v>
+      <c r="B35" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10" t="s">
-        <v>120</v>
+        <v>116</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K35" s="5" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="14">
+      <c r="A36" s="11">
         <v>46192</v>
       </c>
-      <c r="B36" s="11" t="s">
-        <v>180</v>
+      <c r="B36" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>8</v>
+        <v>119</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="K36" s="5" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="14">
+      <c r="A37" s="11">
         <v>46195</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>61</v>
+      <c r="B37" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K37" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="14">
+      <c r="A38" s="11">
         <v>46196</v>
       </c>
-      <c r="B38" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>8</v>
+      <c r="B38" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="K38" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="14">
+      <c r="A39" s="11">
         <v>46197</v>
       </c>
-      <c r="B39" s="11" t="s">
-        <v>130</v>
+      <c r="B39" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E39" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="K39" s="5" t="s">
@@ -1827,195 +1821,197 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="14">
+      <c r="A40" s="11">
         <v>46198</v>
       </c>
-      <c r="B40" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>120</v>
+      <c r="B40" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K40" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" s="14">
+      <c r="A41" s="11">
         <v>46199</v>
       </c>
-      <c r="B41" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>81</v>
+      <c r="B41" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="K41" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A42" s="14">
+      <c r="A42" s="11">
         <v>46202</v>
       </c>
-      <c r="B42" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10" t="s">
-        <v>141</v>
+      <c r="B42" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" s="14">
+      <c r="A43" s="11">
         <v>46203</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>120</v>
+      <c r="B43" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="K43" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="14">
+      <c r="A44" s="11">
         <v>46204</v>
       </c>
-      <c r="B44" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>36</v>
+      <c r="B44" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="K44" s="5" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" s="14">
+      <c r="A45" s="11">
         <v>46205</v>
       </c>
-      <c r="B45" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>150</v>
+      <c r="B45" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K45" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="14">
+      <c r="A46" s="11">
         <v>46206</v>
       </c>
-      <c r="B46" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>14</v>
+      <c r="B46" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="K46" s="5" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A47" s="14">
+      <c r="A47" s="11">
         <v>46209</v>
       </c>
-      <c r="B47" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>157</v>
+      <c r="B47" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="K47" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="14">
+      <c r="A48" s="11">
         <v>46210</v>
       </c>
-      <c r="B48" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>160</v>
+      <c r="B48" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="K48" s="5" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="14">
+      <c r="A49" s="11">
         <v>46211</v>
       </c>
-      <c r="B49" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10" t="s">
+      <c r="B49" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E49" s="4" t="s">
         <v>160</v>
       </c>
       <c r="K49" s="5" t="s">
@@ -2023,19 +2019,17 @@
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="14">
+      <c r="A50" s="11">
         <v>46212</v>
       </c>
-      <c r="B50" s="11" t="s">
-        <v>163</v>
+      <c r="B50" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E50" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4" t="s">
         <v>160</v>
       </c>
       <c r="K50" s="5" t="s">
@@ -2043,274 +2037,274 @@
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="14">
+      <c r="A51" s="11">
         <v>46213</v>
       </c>
-      <c r="B51" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>8</v>
+      <c r="B51" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="K51" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="14">
+      <c r="A52" s="11">
         <v>46216</v>
       </c>
-      <c r="B52" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>47</v>
+      <c r="B52" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="5" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="14">
+      <c r="A53" s="11">
         <v>46217</v>
       </c>
-      <c r="B53" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>36</v>
+      <c r="B53" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="K53" s="5" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="14">
+      <c r="A54" s="11">
         <v>46218</v>
       </c>
-      <c r="B54" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="D54" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>105</v>
+      <c r="B54" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K54" s="5" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="14">
+      <c r="A55" s="11">
         <v>46219</v>
       </c>
-      <c r="B55" s="10" t="s">
-        <v>5</v>
+      <c r="B55" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>8</v>
+        <v>176</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K55" s="5" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="14">
+      <c r="A56" s="11">
         <v>46220</v>
       </c>
-      <c r="B56" s="10" t="s">
-        <v>9</v>
+      <c r="B56" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K56" s="5" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="14">
+      <c r="A57" s="11">
         <v>46223</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="11">
+        <v>46224</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C58" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D58" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E58" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="14">
-        <v>46224</v>
-      </c>
-      <c r="B58" s="10" t="s">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="11">
+        <v>46225</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C59" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D59" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E59" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="14">
-        <v>46225</v>
-      </c>
-      <c r="B59" s="10" t="s">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="11">
+        <v>46226</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C60" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D60" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E60" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="14">
-        <v>46226</v>
-      </c>
-      <c r="B60" s="10" t="s">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="11">
+        <v>46230</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C61" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D61" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E60" s="10"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="14">
-        <v>46230</v>
-      </c>
-      <c r="B61" s="10" t="s">
+      <c r="E61" s="4"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="11">
+        <v>46231</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C62" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D62" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E62" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="14">
-        <v>46231</v>
-      </c>
-      <c r="B62" s="10" t="s">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" s="11">
+        <v>46232</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C63" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D63" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E63" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="14">
-        <v>46232</v>
-      </c>
-      <c r="B63" s="10" t="s">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" s="11">
+        <v>46233</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C64" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D64" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="E64" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="14">
-        <v>46233</v>
-      </c>
-      <c r="B64" s="10" t="s">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="11">
+        <v>46234</v>
+      </c>
+      <c r="B65" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C65" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D64" s="10" t="s">
+      <c r="D65" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E64" s="10" t="s">
+      <c r="E65" s="4" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="14">
-        <v>46234</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/lista.xlsx
+++ b/lista.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b13b68726d4d8989/ARCHIVOS XAVIER/APS/Virgen Maria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{5C7F9D3D-B469-4DD7-AE72-59DFFA54B49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4543360-9C8E-443C-B711-9807BF2EB0D3}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{5C7F9D3D-B469-4DD7-AE72-59DFFA54B49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91838B95-692F-4AF5-B455-21CEE046AA0C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B8ADF1EA-8CC5-4C57-B17E-5279ED80BB0E}"/>
   </bookViews>
@@ -1052,8 +1052,7 @@
     <col min="3" max="3" width="22.6640625" customWidth="1"/>
     <col min="4" max="4" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="63.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" customWidth="1"/>
-    <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1073,6 +1072,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="11">
@@ -2178,13 +2178,13 @@
         <v>46224</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>16</v>
+        <v>185</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>14</v>
@@ -2195,16 +2195,16 @@
         <v>46225</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
@@ -2212,16 +2212,16 @@
         <v>46226</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
@@ -2229,45 +2229,45 @@
         <v>46230</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E61" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="11">
         <v>46231</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>14</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E62" s="4"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="11">
         <v>46232</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>183</v>
+        <v>30</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>14</v>
@@ -2278,16 +2278,16 @@
         <v>46233</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -2295,16 +2295,16 @@
         <v>46234</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/lista.xlsx
+++ b/lista.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b13b68726d4d8989/ARCHIVOS XAVIER/APS/Virgen Maria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{5C7F9D3D-B469-4DD7-AE72-59DFFA54B49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B869CB7-9256-40D8-9ED1-B6F84E125CBD}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{5C7F9D3D-B469-4DD7-AE72-59DFFA54B49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72114B1E-9B7E-4729-976F-DC65DF05D271}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B8ADF1EA-8CC5-4C57-B17E-5279ED80BB0E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="182">
   <si>
     <t>Fecha</t>
   </si>
@@ -576,6 +576,15 @@
   </si>
   <si>
     <t>rosaura_katty@hotmail.com</t>
+  </si>
+  <si>
+    <t>0992143462</t>
+  </si>
+  <si>
+    <t>WENDY VILLAVICIENCIO</t>
+  </si>
+  <si>
+    <t>0980447454</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92574074-88DB-4446-9761-6F1FEA06A5BF}">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K181"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="5" customWidth="1"/>
@@ -1055,19 +1064,19 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="10">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>5</v>
@@ -1075,19 +1084,19 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>9</v>
@@ -1095,17 +1104,19 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D4" s="3"/>
+        <v>129</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="E4" s="3" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>13</v>
@@ -1113,16 +1124,16 @@
     </row>
     <row r="5" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>118</v>
@@ -1133,19 +1144,19 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>18</v>
@@ -1153,19 +1164,17 @@
     </row>
     <row r="7" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>147</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>22</v>
@@ -1173,19 +1182,19 @@
     </row>
     <row r="8" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>25</v>
@@ -1193,19 +1202,19 @@
     </row>
     <row r="9" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>155</v>
+        <v>36</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>28</v>
@@ -1213,19 +1222,19 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>31</v>
@@ -1233,17 +1242,19 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" s="3"/>
+        <v>150</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="E11" s="3" t="s">
-        <v>158</v>
+        <v>14</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>33</v>
@@ -1251,19 +1262,19 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>37</v>
@@ -1271,19 +1282,19 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>41</v>
@@ -1291,19 +1302,17 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>169</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>45</v>
+        <v>158</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>44</v>
@@ -1311,19 +1320,19 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>158</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>46</v>
@@ -1331,16 +1340,16 @@
     </row>
     <row r="16" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>5</v>
+        <v>164</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>7</v>
+        <v>166</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>8</v>
@@ -1351,19 +1360,19 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>9</v>
+        <v>167</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>51</v>
@@ -1371,19 +1380,19 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>17</v>
+        <v>172</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>54</v>
@@ -1391,39 +1400,35 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
       <c r="K19" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>60</v>
@@ -1431,34 +1436,36 @@
     </row>
     <row r="21" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="K21" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>14</v>
@@ -1469,19 +1476,19 @@
     </row>
     <row r="23" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>70</v>
@@ -1489,19 +1496,19 @@
     </row>
     <row r="24" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>73</v>
@@ -1509,39 +1516,37 @@
     </row>
     <row r="25" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E25" s="3"/>
       <c r="K25" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>77</v>
@@ -1549,19 +1554,19 @@
     </row>
     <row r="27" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>11</v>
+        <v>178</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>80</v>
@@ -1569,19 +1574,19 @@
     </row>
     <row r="28" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>82</v>
@@ -1589,19 +1594,19 @@
     </row>
     <row r="29" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>85</v>
@@ -1609,17 +1614,19 @@
     </row>
     <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="7">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E30" s="3" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>88</v>
@@ -1627,19 +1634,19 @@
     </row>
     <row r="31" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>91</v>
@@ -1647,19 +1654,19 @@
     </row>
     <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>94</v>
@@ -1667,19 +1674,19 @@
     </row>
     <row r="33" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>97</v>
@@ -1687,37 +1694,37 @@
     </row>
     <row r="34" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E34" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="K34" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>104</v>
@@ -1725,19 +1732,19 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>108</v>
@@ -1745,17 +1752,19 @@
     </row>
     <row r="37" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" s="3"/>
+        <v>64</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="E37" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>15</v>
@@ -1763,37 +1772,37 @@
     </row>
     <row r="38" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="3"/>
       <c r="K38" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>22</v>
@@ -1801,17 +1810,19 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D40" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="E40" s="3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>25</v>
@@ -1819,17 +1830,15 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>90</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
         <v>79</v>
       </c>
@@ -1839,17 +1848,15 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>93</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
         <v>79</v>
       </c>
@@ -1859,16 +1866,16 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>79</v>
@@ -1879,19 +1886,17 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>99</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>111</v>
@@ -1899,19 +1904,19 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>41</v>
@@ -1919,19 +1924,19 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>112</v>
@@ -1939,19 +1944,19 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>44</v>
@@ -1959,19 +1964,19 @@
     </row>
     <row r="48" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>47</v>
@@ -1979,19 +1984,19 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>54</v>
@@ -1999,17 +2004,19 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D50" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="E50" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>51</v>
@@ -2017,19 +2024,19 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>113</v>
@@ -2037,19 +2044,19 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>116</v>
@@ -2057,16 +2064,16 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>8</v>
@@ -2077,19 +2084,17 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>130</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>122</v>
@@ -2097,19 +2102,19 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="10">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>125</v>
@@ -2117,19 +2122,19 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>128</v>
@@ -2137,332 +2142,328 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D57" s="3"/>
+        <v>126</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>127</v>
+      </c>
       <c r="E57" s="3" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="10">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>148</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="10">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>151</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D61" s="3"/>
       <c r="E61" s="3" t="s">
-        <v>14</v>
+        <v>139</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D64" s="3"/>
+        <v>146</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="E64" s="3" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>158</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="12">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="B66" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C66" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D66" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E66" t="s">
-        <v>8</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="12">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B67" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C67" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D67" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E67" t="s">
-        <v>45</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="12">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="B68" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C68" t="s">
-        <v>171</v>
-      </c>
-      <c r="D68" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="E68" t="s">
-        <v>103</v>
+        <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="12">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="B69" t="s">
-        <v>5</v>
+        <v>161</v>
       </c>
       <c r="C69" t="s">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="D69" t="s">
-        <v>7</v>
+        <v>163</v>
       </c>
       <c r="E69" t="s">
-        <v>8</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="12">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>164</v>
       </c>
       <c r="C70" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D70" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="E70" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="12">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="D71" t="s">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="E71" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="12">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="D72" t="s">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="12">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="B73" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="C73" t="s">
-        <v>23</v>
-      </c>
-      <c r="D73" t="s">
-        <v>24</v>
-      </c>
-      <c r="E73" t="s">
-        <v>14</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="12">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="B74" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C74" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D74" t="s">
-        <v>27</v>
+        <v>7</v>
+      </c>
+      <c r="E74" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="12">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B75" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c r="D75" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="12">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B76" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D76" t="s">
-        <v>178</v>
+        <v>17</v>
       </c>
       <c r="E76" t="s">
         <v>14</v>
@@ -2470,307 +2471,310 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="12">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="B77" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D77" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E77" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="12">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="B78" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C78" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D78" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E78" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="12">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="B79" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D79" t="s">
-        <v>43</v>
-      </c>
-      <c r="E79" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="12">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C80" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D80" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E80" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="12">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="B81" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C81" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D81" t="s">
-        <v>49</v>
+        <v>178</v>
       </c>
       <c r="E81" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="12">
-        <v>46317</v>
+        <v>46321</v>
       </c>
       <c r="B82" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C82" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D82" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E82" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="12">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="B83" t="s">
-        <v>54</v>
-      </c>
-      <c r="C83">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="C83" t="s">
+        <v>38</v>
+      </c>
+      <c r="D83" t="s">
+        <v>39</v>
       </c>
       <c r="E83" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="12">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C84" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D84" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E84" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="12">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="B85" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="C85" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="D85" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="E85" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="12">
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="B86" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C86" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D86" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E86" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="12">
-        <v>46324</v>
+        <v>46330</v>
       </c>
       <c r="B87" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C87" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D87" t="s">
-        <v>69</v>
+        <v>53</v>
+      </c>
+      <c r="E87" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="12">
-        <v>46325</v>
+        <v>46331</v>
       </c>
       <c r="B88" t="s">
-        <v>70</v>
-      </c>
-      <c r="C88" t="s">
-        <v>71</v>
-      </c>
-      <c r="D88" t="s">
-        <v>72</v>
+        <v>54</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="12">
-        <v>46330</v>
+        <v>46332</v>
       </c>
       <c r="B89" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C89" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D89" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E89" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="12">
-        <v>46331</v>
+        <v>46335</v>
       </c>
       <c r="B90" t="s">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="C90" t="s">
-        <v>78</v>
+        <v>61</v>
+      </c>
+      <c r="D90" t="s">
+        <v>62</v>
       </c>
       <c r="E90" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="12">
-        <v>46332</v>
+        <v>46336</v>
       </c>
       <c r="B91" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C91" t="s">
-        <v>81</v>
+        <v>64</v>
+      </c>
+      <c r="D91" t="s">
+        <v>65</v>
       </c>
       <c r="E91" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="12">
-        <v>46335</v>
+        <v>46337</v>
       </c>
       <c r="B92" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C92" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D92" t="s">
-        <v>84</v>
-      </c>
-      <c r="E92" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="12">
-        <v>46336</v>
+        <v>46338</v>
       </c>
       <c r="B93" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C93" t="s">
-        <v>86</v>
+        <v>71</v>
+      </c>
+      <c r="D93" t="s">
+        <v>72</v>
       </c>
       <c r="E93" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="12">
-        <v>46337</v>
+        <v>46339</v>
       </c>
       <c r="B94" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C94" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D94" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E94" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="12">
-        <v>46338</v>
+        <v>46342</v>
       </c>
       <c r="B95" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C95" t="s">
-        <v>92</v>
-      </c>
-      <c r="D95" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E95" t="s">
         <v>79</v>
@@ -2778,16 +2782,13 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="12">
-        <v>46339</v>
+        <v>46343</v>
       </c>
       <c r="B96" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C96" t="s">
-        <v>95</v>
-      </c>
-      <c r="D96" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E96" t="s">
         <v>79</v>
@@ -2795,16 +2796,16 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="12">
-        <v>46342</v>
+        <v>46344</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D97" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E97" t="s">
         <v>79</v>
@@ -2812,166 +2813,166 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="12">
-        <v>46343</v>
+        <v>46345</v>
       </c>
       <c r="B98" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C98" t="s">
-        <v>101</v>
-      </c>
-      <c r="D98" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="E98" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="12">
-        <v>46344</v>
+        <v>46346</v>
       </c>
       <c r="B99" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C99" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D99" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E99" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="12">
-        <v>46345</v>
+        <v>46349</v>
       </c>
       <c r="B100" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C100" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="D100" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="E100" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="12">
-        <v>46346</v>
+        <v>46350</v>
       </c>
       <c r="B101" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C101" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="D101" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="E101" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="12">
-        <v>46349</v>
+        <v>46351</v>
       </c>
       <c r="B102" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C102" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D102" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E102" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="12">
-        <v>46350</v>
+        <v>46352</v>
       </c>
       <c r="B103" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="C103" t="s">
-        <v>117</v>
+        <v>101</v>
+      </c>
+      <c r="D103" t="s">
+        <v>102</v>
       </c>
       <c r="E103" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="12">
-        <v>46351</v>
+        <v>46353</v>
       </c>
       <c r="B104" t="s">
-        <v>175</v>
+        <v>104</v>
       </c>
       <c r="C104" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D104" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="E104" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="12">
-        <v>46352</v>
+        <v>46356</v>
       </c>
       <c r="B105" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C105" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D105" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="E105" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="12">
-        <v>46353</v>
+        <v>46357</v>
       </c>
       <c r="B106" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="C106" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="D106" t="s">
-        <v>127</v>
+        <v>39</v>
       </c>
       <c r="E106" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="12">
-        <v>46356</v>
+        <v>46358</v>
       </c>
       <c r="B107" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C107" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -2979,16 +2980,13 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="12">
-        <v>46357</v>
+        <v>46359</v>
       </c>
       <c r="B108" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C108" t="s">
-        <v>132</v>
-      </c>
-      <c r="D108" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="E108" t="s">
         <v>118</v>
@@ -2996,350 +2994,1198 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="12">
-        <v>46358</v>
+        <v>46360</v>
       </c>
       <c r="B109" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="C109" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D109" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E109" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="12">
-        <v>46359</v>
+        <v>46363</v>
       </c>
       <c r="B110" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C110" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+      <c r="D110" t="s">
+        <v>124</v>
       </c>
       <c r="E110" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="12">
-        <v>46360</v>
+        <v>46364</v>
       </c>
       <c r="B111" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C111" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D111" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E111" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="12">
-        <v>46363</v>
+        <v>46365</v>
       </c>
       <c r="B112" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="C112" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D112" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="E112" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="12">
-        <v>46364</v>
+        <v>46366</v>
       </c>
       <c r="B113" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="C113" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D113" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E113" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="12">
-        <v>46365</v>
+        <v>46367</v>
       </c>
       <c r="B114" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C114" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D114" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="E114" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="12">
-        <v>46366</v>
+        <v>46370</v>
       </c>
       <c r="B115" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C115" t="s">
-        <v>153</v>
-      </c>
-      <c r="D115" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="E115" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="12">
-        <v>46367</v>
+        <v>46371</v>
       </c>
       <c r="B116" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="C116" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="D116" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="E116" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="12">
-        <v>46370</v>
+        <v>46372</v>
       </c>
       <c r="B117" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C117" t="s">
-        <v>160</v>
+        <v>143</v>
+      </c>
+      <c r="D117" t="s">
+        <v>144</v>
       </c>
       <c r="E117" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="12">
-        <v>46371</v>
+        <v>46373</v>
       </c>
       <c r="B118" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="C118" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="D118" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="E118" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="12">
-        <v>46372</v>
+        <v>46374</v>
       </c>
       <c r="B119" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C119" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D119" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="E119" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="12">
-        <v>46373</v>
+        <v>46377</v>
       </c>
       <c r="B120" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="C120" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="D120" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="E120" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="12">
-        <v>46374</v>
+        <v>46378</v>
       </c>
       <c r="B121" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C121" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D121" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E121" t="s">
-        <v>103</v>
+        <v>158</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="12">
-        <v>46377</v>
+        <v>46379</v>
       </c>
       <c r="B122" t="s">
-        <v>5</v>
+        <v>159</v>
       </c>
       <c r="C122" t="s">
-        <v>6</v>
-      </c>
-      <c r="D122" t="s">
-        <v>7</v>
+        <v>160</v>
       </c>
       <c r="E122" t="s">
-        <v>8</v>
+        <v>158</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="12">
-        <v>46378</v>
+        <v>46380</v>
       </c>
       <c r="B123" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C123" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D123" t="s">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="E123" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="12">
-        <v>46379</v>
+        <v>46384</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>164</v>
       </c>
       <c r="C124" t="s">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="D124" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="E124" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="12">
-        <v>46380</v>
+        <v>46385</v>
       </c>
       <c r="B125" t="s">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="C125" t="s">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="D125" t="s">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="E125" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="12">
-        <v>46384</v>
+        <v>46386</v>
       </c>
       <c r="B126" t="s">
-        <v>22</v>
+        <v>170</v>
       </c>
       <c r="C126" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
       <c r="D126" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="E126" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="12">
-        <v>46385</v>
+        <v>46387</v>
       </c>
       <c r="B127" t="s">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="C127" t="s">
-        <v>26</v>
-      </c>
-      <c r="D127" t="s">
-        <v>27</v>
+        <v>181</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="12">
-        <v>46386</v>
+        <v>46391</v>
       </c>
       <c r="B128" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C128" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E128" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="12">
-        <v>46387</v>
+        <v>46392</v>
       </c>
       <c r="B129" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" t="s">
+        <v>173</v>
+      </c>
+      <c r="D129" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="12">
+        <v>46393</v>
+      </c>
+      <c r="B130" t="s">
+        <v>15</v>
+      </c>
+      <c r="C130" t="s">
+        <v>16</v>
+      </c>
+      <c r="D130" t="s">
+        <v>17</v>
+      </c>
+      <c r="E130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="12">
+        <v>46394</v>
+      </c>
+      <c r="B131" t="s">
+        <v>18</v>
+      </c>
+      <c r="C131" t="s">
+        <v>19</v>
+      </c>
+      <c r="D131" t="s">
+        <v>20</v>
+      </c>
+      <c r="E131" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="12">
+        <v>46395</v>
+      </c>
+      <c r="B132" t="s">
+        <v>22</v>
+      </c>
+      <c r="C132" t="s">
+        <v>23</v>
+      </c>
+      <c r="D132" t="s">
+        <v>24</v>
+      </c>
+      <c r="E132" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="12">
+        <v>46398</v>
+      </c>
+      <c r="B133" t="s">
+        <v>25</v>
+      </c>
+      <c r="C133" t="s">
+        <v>26</v>
+      </c>
+      <c r="D133" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="12">
+        <v>46399</v>
+      </c>
+      <c r="B134" t="s">
+        <v>28</v>
+      </c>
+      <c r="C134" t="s">
+        <v>29</v>
+      </c>
+      <c r="D134" t="s">
+        <v>30</v>
+      </c>
+      <c r="E134" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="12">
+        <v>46400</v>
+      </c>
+      <c r="B135" t="s">
         <v>31</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C135" t="s">
         <v>32</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D135" t="s">
         <v>178</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E135" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="12">
+        <v>46401</v>
+      </c>
+      <c r="B136" t="s">
+        <v>33</v>
+      </c>
+      <c r="C136" t="s">
+        <v>34</v>
+      </c>
+      <c r="D136" t="s">
+        <v>35</v>
+      </c>
+      <c r="E136" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" s="12">
+        <v>46402</v>
+      </c>
+      <c r="B137" t="s">
+        <v>37</v>
+      </c>
+      <c r="C137" t="s">
+        <v>38</v>
+      </c>
+      <c r="D137" t="s">
+        <v>39</v>
+      </c>
+      <c r="E137" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="12">
+        <v>46405</v>
+      </c>
+      <c r="B138" t="s">
+        <v>41</v>
+      </c>
+      <c r="C138" t="s">
+        <v>42</v>
+      </c>
+      <c r="D138" t="s">
+        <v>43</v>
+      </c>
+      <c r="E138" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="12">
+        <v>46406</v>
+      </c>
+      <c r="B139" t="s">
+        <v>46</v>
+      </c>
+      <c r="C139" t="s">
+        <v>10</v>
+      </c>
+      <c r="D139" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" s="12">
+        <v>46407</v>
+      </c>
+      <c r="B140" t="s">
+        <v>47</v>
+      </c>
+      <c r="C140" t="s">
+        <v>48</v>
+      </c>
+      <c r="D140" t="s">
+        <v>49</v>
+      </c>
+      <c r="E140" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="12">
+        <v>46408</v>
+      </c>
+      <c r="B141" t="s">
+        <v>51</v>
+      </c>
+      <c r="C141" t="s">
+        <v>52</v>
+      </c>
+      <c r="D141" t="s">
+        <v>53</v>
+      </c>
+      <c r="E141" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" s="12">
+        <v>46409</v>
+      </c>
+      <c r="B142" t="s">
+        <v>54</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="E142" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="12">
+        <v>46412</v>
+      </c>
+      <c r="B143" t="s">
+        <v>56</v>
+      </c>
+      <c r="C143" t="s">
+        <v>57</v>
+      </c>
+      <c r="D143" t="s">
+        <v>58</v>
+      </c>
+      <c r="E143" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="12">
+        <v>46413</v>
+      </c>
+      <c r="B144" t="s">
+        <v>174</v>
+      </c>
+      <c r="C144" t="s">
+        <v>61</v>
+      </c>
+      <c r="D144" t="s">
+        <v>62</v>
+      </c>
+      <c r="E144" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" s="12">
+        <v>46414</v>
+      </c>
+      <c r="B145" t="s">
+        <v>63</v>
+      </c>
+      <c r="C145" t="s">
+        <v>64</v>
+      </c>
+      <c r="D145" t="s">
+        <v>65</v>
+      </c>
+      <c r="E145" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="12">
+        <v>46415</v>
+      </c>
+      <c r="B146" t="s">
+        <v>67</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" s="12">
+        <v>46416</v>
+      </c>
+      <c r="B147" t="s">
+        <v>70</v>
+      </c>
+      <c r="C147" t="s">
+        <v>71</v>
+      </c>
+      <c r="D147" t="s">
+        <v>72</v>
+      </c>
+      <c r="E147" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" s="12">
+        <v>46419</v>
+      </c>
+      <c r="B148" t="s">
+        <v>73</v>
+      </c>
+      <c r="C148" t="s">
+        <v>74</v>
+      </c>
+      <c r="D148" t="s">
+        <v>75</v>
+      </c>
+      <c r="E148" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" s="12">
+        <v>46420</v>
+      </c>
+      <c r="B149" t="s">
+        <v>77</v>
+      </c>
+      <c r="C149" t="s">
+        <v>78</v>
+      </c>
+      <c r="E149" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" s="12">
+        <v>46421</v>
+      </c>
+      <c r="B150" t="s">
+        <v>80</v>
+      </c>
+      <c r="C150" t="s">
+        <v>81</v>
+      </c>
+      <c r="E150" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" s="12">
+        <v>46422</v>
+      </c>
+      <c r="B151" t="s">
+        <v>82</v>
+      </c>
+      <c r="C151" t="s">
+        <v>83</v>
+      </c>
+      <c r="D151" t="s">
+        <v>84</v>
+      </c>
+      <c r="E151" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" s="12">
+        <v>46423</v>
+      </c>
+      <c r="B152" t="s">
+        <v>85</v>
+      </c>
+      <c r="C152" t="s">
+        <v>86</v>
+      </c>
+      <c r="E152" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" s="12">
+        <v>46428</v>
+      </c>
+      <c r="B153" t="s">
+        <v>88</v>
+      </c>
+      <c r="C153" t="s">
+        <v>89</v>
+      </c>
+      <c r="D153" t="s">
+        <v>90</v>
+      </c>
+      <c r="E153" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" s="12">
+        <v>46429</v>
+      </c>
+      <c r="B154" t="s">
+        <v>91</v>
+      </c>
+      <c r="C154" t="s">
+        <v>92</v>
+      </c>
+      <c r="D154" t="s">
+        <v>93</v>
+      </c>
+      <c r="E154" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155" s="12">
+        <v>46430</v>
+      </c>
+      <c r="B155" t="s">
+        <v>94</v>
+      </c>
+      <c r="C155" t="s">
+        <v>95</v>
+      </c>
+      <c r="D155" t="s">
+        <v>96</v>
+      </c>
+      <c r="E155" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" s="12">
+        <v>46433</v>
+      </c>
+      <c r="B156" t="s">
+        <v>97</v>
+      </c>
+      <c r="C156" t="s">
+        <v>98</v>
+      </c>
+      <c r="D156" t="s">
+        <v>99</v>
+      </c>
+      <c r="E156" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" s="12">
+        <v>46434</v>
+      </c>
+      <c r="B157" t="s">
+        <v>100</v>
+      </c>
+      <c r="C157" t="s">
+        <v>101</v>
+      </c>
+      <c r="D157" t="s">
+        <v>102</v>
+      </c>
+      <c r="E157" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" s="12">
+        <v>46435</v>
+      </c>
+      <c r="B158" t="s">
+        <v>104</v>
+      </c>
+      <c r="C158" t="s">
+        <v>105</v>
+      </c>
+      <c r="D158" t="s">
+        <v>106</v>
+      </c>
+      <c r="E158" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" s="12">
+        <v>46436</v>
+      </c>
+      <c r="B159" t="s">
+        <v>108</v>
+      </c>
+      <c r="C159" t="s">
+        <v>109</v>
+      </c>
+      <c r="D159" t="s">
+        <v>110</v>
+      </c>
+      <c r="E159" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" s="12">
+        <v>46437</v>
+      </c>
+      <c r="B160" t="s">
+        <v>111</v>
+      </c>
+      <c r="C160" t="s">
+        <v>38</v>
+      </c>
+      <c r="D160" t="s">
+        <v>39</v>
+      </c>
+      <c r="E160" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161" s="12">
+        <v>46440</v>
+      </c>
+      <c r="B161" t="s">
+        <v>113</v>
+      </c>
+      <c r="C161" t="s">
+        <v>114</v>
+      </c>
+      <c r="D161" t="s">
+        <v>115</v>
+      </c>
+      <c r="E161" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162" s="12">
+        <v>46441</v>
+      </c>
+      <c r="B162" t="s">
+        <v>116</v>
+      </c>
+      <c r="C162" t="s">
+        <v>117</v>
+      </c>
+      <c r="E162" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163" s="12">
+        <v>46442</v>
+      </c>
+      <c r="B163" t="s">
+        <v>175</v>
+      </c>
+      <c r="C163" t="s">
+        <v>120</v>
+      </c>
+      <c r="D163" t="s">
+        <v>121</v>
+      </c>
+      <c r="E163" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" s="12">
+        <v>46443</v>
+      </c>
+      <c r="B164" t="s">
+        <v>122</v>
+      </c>
+      <c r="C164" t="s">
+        <v>123</v>
+      </c>
+      <c r="D164" t="s">
+        <v>124</v>
+      </c>
+      <c r="E164" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" s="12">
+        <v>46444</v>
+      </c>
+      <c r="B165" t="s">
+        <v>125</v>
+      </c>
+      <c r="C165" t="s">
+        <v>126</v>
+      </c>
+      <c r="D165" t="s">
+        <v>127</v>
+      </c>
+      <c r="E165" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" s="12">
+        <v>46447</v>
+      </c>
+      <c r="B166" t="s">
+        <v>128</v>
+      </c>
+      <c r="C166" t="s">
+        <v>129</v>
+      </c>
+      <c r="D166" t="s">
+        <v>130</v>
+      </c>
+      <c r="E166" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" s="12">
+        <v>46448</v>
+      </c>
+      <c r="B167" t="s">
+        <v>131</v>
+      </c>
+      <c r="C167" t="s">
+        <v>132</v>
+      </c>
+      <c r="D167" t="s">
+        <v>133</v>
+      </c>
+      <c r="E167" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168" s="12">
+        <v>46449</v>
+      </c>
+      <c r="B168" t="s">
+        <v>134</v>
+      </c>
+      <c r="C168" t="s">
+        <v>135</v>
+      </c>
+      <c r="D168" t="s">
+        <v>136</v>
+      </c>
+      <c r="E168" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169" s="12">
+        <v>46450</v>
+      </c>
+      <c r="B169" t="s">
+        <v>137</v>
+      </c>
+      <c r="C169" t="s">
+        <v>138</v>
+      </c>
+      <c r="E169" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" s="12">
+        <v>46451</v>
+      </c>
+      <c r="B170" t="s">
+        <v>140</v>
+      </c>
+      <c r="C170" t="s">
+        <v>141</v>
+      </c>
+      <c r="D170" t="s">
+        <v>142</v>
+      </c>
+      <c r="E170" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="12">
+        <v>46454</v>
+      </c>
+      <c r="B171" t="s">
+        <v>176</v>
+      </c>
+      <c r="C171" t="s">
+        <v>143</v>
+      </c>
+      <c r="D171" t="s">
+        <v>144</v>
+      </c>
+      <c r="E171" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="12">
+        <v>46455</v>
+      </c>
+      <c r="B172" t="s">
+        <v>145</v>
+      </c>
+      <c r="C172" t="s">
+        <v>146</v>
+      </c>
+      <c r="D172" t="s">
+        <v>147</v>
+      </c>
+      <c r="E172" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" s="12">
+        <v>46456</v>
+      </c>
+      <c r="B173" t="s">
+        <v>149</v>
+      </c>
+      <c r="C173" t="s">
+        <v>150</v>
+      </c>
+      <c r="D173" t="s">
+        <v>151</v>
+      </c>
+      <c r="E173" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" s="12">
+        <v>46457</v>
+      </c>
+      <c r="B174" t="s">
+        <v>152</v>
+      </c>
+      <c r="C174" t="s">
+        <v>153</v>
+      </c>
+      <c r="D174" t="s">
+        <v>154</v>
+      </c>
+      <c r="E174" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" s="12">
+        <v>46458</v>
+      </c>
+      <c r="B175" t="s">
+        <v>177</v>
+      </c>
+      <c r="C175" t="s">
+        <v>156</v>
+      </c>
+      <c r="D175" t="s">
+        <v>157</v>
+      </c>
+      <c r="E175" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" s="12">
+        <v>46461</v>
+      </c>
+      <c r="B176" t="s">
+        <v>159</v>
+      </c>
+      <c r="C176" t="s">
+        <v>179</v>
+      </c>
+      <c r="E176" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177" s="12">
+        <v>46462</v>
+      </c>
+      <c r="B177" t="s">
+        <v>161</v>
+      </c>
+      <c r="C177" t="s">
+        <v>162</v>
+      </c>
+      <c r="D177" t="s">
+        <v>163</v>
+      </c>
+      <c r="E177" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" s="12">
+        <v>46463</v>
+      </c>
+      <c r="B178" t="s">
+        <v>164</v>
+      </c>
+      <c r="C178" t="s">
+        <v>165</v>
+      </c>
+      <c r="D178" t="s">
+        <v>166</v>
+      </c>
+      <c r="E178" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179" s="12">
+        <v>46464</v>
+      </c>
+      <c r="B179" t="s">
+        <v>167</v>
+      </c>
+      <c r="C179" t="s">
+        <v>168</v>
+      </c>
+      <c r="D179" t="s">
+        <v>169</v>
+      </c>
+      <c r="E179" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" s="12">
+        <v>46465</v>
+      </c>
+      <c r="B180" t="s">
+        <v>170</v>
+      </c>
+      <c r="C180" t="s">
+        <v>171</v>
+      </c>
+      <c r="D180" t="s">
+        <v>172</v>
+      </c>
+      <c r="E180" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A181" s="12">
+        <v>46468</v>
+      </c>
+      <c r="B181" t="s">
+        <v>180</v>
+      </c>
+      <c r="C181" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
